--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48051,6 +48051,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2074">
+      <c r="A2074" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2074" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2074" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>0.98199999332428</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G2074" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48074,6 +48074,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2075" t="n">
+        <v>20400</v>
+      </c>
+      <c r="C2075" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>0.977999985218048</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G2075" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48097,6 +48097,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2076">
+      <c r="A2076" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2076" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C2076" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G2076" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48120,6 +48120,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2077">
+      <c r="A2077" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2077" t="n">
+        <v>450</v>
+      </c>
+      <c r="C2077" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G2077" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -47961,22 +47961,22 @@
     </row>
     <row r="2070">
       <c r="A2070" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2070" t="n">
-        <v>2850</v>
+        <v>8400</v>
       </c>
       <c r="C2070" t="n">
-        <v>1.04999995231628</v>
+        <v>1.05999994277954</v>
       </c>
       <c r="D2070" t="n">
-        <v>1.01999998092651</v>
+        <v>1.01499998569489</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.01999998092651</v>
+        <v>1.01499998569489</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.04999995231628</v>
+        <v>1.05999994277954</v>
       </c>
       <c r="G2070" t="s">
         <v>7</v>
@@ -47984,19 +47984,19 @@
     </row>
     <row r="2071">
       <c r="A2071" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2071" t="n">
-        <v>0</v>
+        <v>2850</v>
       </c>
       <c r="C2071" t="n">
         <v>1.04999995231628</v>
       </c>
       <c r="D2071" t="n">
-        <v>1.04999995231628</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.04999995231628</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="F2071" t="n">
         <v>1.04999995231628</v>
@@ -48007,22 +48007,22 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2072" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="C2072" t="n">
-        <v>1.01499998569489</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="D2072" t="n">
-        <v>1</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.01499998569489</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="F2072" t="n">
-        <v>1</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="G2072" t="s">
         <v>7</v>
@@ -48030,22 +48030,22 @@
     </row>
     <row r="2073">
       <c r="A2073" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2073" t="n">
-        <v>4800</v>
+        <v>3300</v>
       </c>
       <c r="C2073" t="n">
-        <v>1.00999999046326</v>
+        <v>1.01499998569489</v>
       </c>
       <c r="D2073" t="n">
-        <v>0.955999970436096</v>
+        <v>1</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.00999999046326</v>
+        <v>1.01499998569489</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.980000019073486</v>
+        <v>1</v>
       </c>
       <c r="G2073" t="s">
         <v>7</v>
@@ -48053,22 +48053,22 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2074" t="n">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="C2074" t="n">
-        <v>1.02999997138977</v>
+        <v>1.00999999046326</v>
       </c>
       <c r="D2074" t="n">
+        <v>0.955999970436096</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F2074" t="n">
         <v>0.980000019073486</v>
-      </c>
-      <c r="E2074" t="n">
-        <v>0.98199999332428</v>
-      </c>
-      <c r="F2074" t="n">
-        <v>1.02999997138977</v>
       </c>
       <c r="G2074" t="s">
         <v>7</v>
@@ -48076,22 +48076,22 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2075" t="n">
-        <v>20400</v>
+        <v>1800</v>
       </c>
       <c r="C2075" t="n">
         <v>1.02999997138977</v>
       </c>
       <c r="D2075" t="n">
-        <v>0.977999985218048</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="E2075" t="n">
-        <v>1</v>
+        <v>0.98199999332428</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.01999998092651</v>
+        <v>1.02999997138977</v>
       </c>
       <c r="G2075" t="s">
         <v>7</v>
@@ -48099,22 +48099,22 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2076" t="n">
-        <v>5400</v>
+        <v>20400</v>
       </c>
       <c r="C2076" t="n">
-        <v>1.05499994754791</v>
+        <v>1.02999997138977</v>
       </c>
       <c r="D2076" t="n">
-        <v>0.986000001430511</v>
+        <v>0.977999985218048</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.05499994754791</v>
+        <v>1</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.990000009536743</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="G2076" t="s">
         <v>7</v>
@@ -48122,24 +48122,47 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2077" t="n">
-        <v>450</v>
+        <v>5400</v>
       </c>
       <c r="C2077" t="n">
-        <v>1.01999998092651</v>
+        <v>1.05499994754791</v>
       </c>
       <c r="D2077" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="F2077" t="n">
         <v>0.990000009536743</v>
       </c>
-      <c r="E2077" t="n">
+      <c r="G2077" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>22800</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="F2078" t="n">
         <v>0.990000009536743</v>
       </c>
-      <c r="F2077" t="n">
-        <v>1.01999998092651</v>
-      </c>
-      <c r="G2077" t="s">
+      <c r="G2078" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -54455,6 +54455,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="H2081" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -54481,6 +54481,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>3450</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="H2082" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -54507,6 +54507,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="H2083" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -54533,6 +54533,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>11100</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>0.976000010967255</v>
+      </c>
+      <c r="H2084" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48320,7 +48320,9 @@
       <c r="E2085" t="n">
         <v>0.970000028610229</v>
       </c>
-      <c r="F2085"/>
+      <c r="F2085" t="n">
+        <v>1</v>
+      </c>
       <c r="G2085" t="s">
         <v>7</v>
       </c>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48419,6 +48419,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2090">
+      <c r="A2090" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G2090" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>0.96399998664856</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0.934000015258789</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>0.934000015258789</v>
+      </c>
+      <c r="F2091"/>
+      <c r="G2091" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48458,8 +48458,31 @@
       <c r="E2091" t="n">
         <v>0.934000015258789</v>
       </c>
-      <c r="F2091"/>
+      <c r="F2091" t="n">
+        <v>0.96399998664856</v>
+      </c>
       <c r="G2091" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2092" t="n">
+        <v>900</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F2092"/>
+      <c r="G2092" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48481,8 +48481,31 @@
       <c r="E2092" t="n">
         <v>0.990000009536743</v>
       </c>
-      <c r="F2092"/>
+      <c r="F2092" t="n">
+        <v>0.970000028610229</v>
+      </c>
       <c r="G2092" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2093" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>0.96399998664856</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>0.955999970436096</v>
+      </c>
+      <c r="F2093"/>
+      <c r="G2093" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48504,7 +48504,9 @@
       <c r="E2093" t="n">
         <v>0.955999970436096</v>
       </c>
-      <c r="F2093"/>
+      <c r="F2093" t="n">
+        <v>0.96399998664856</v>
+      </c>
       <c r="G2093" t="s">
         <v>7</v>
       </c>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -48534,6 +48534,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2095">
+      <c r="A2095" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>0.938000023365021</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>0.938000023365021</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="G2095" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -54897,6 +54897,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2098">
+      <c r="A2098" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>4650</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0.885999977588654</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>0.885999977588654</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>0.885999977588654</v>
+      </c>
+      <c r="H2098" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -54923,6 +54923,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2099">
+      <c r="A2099" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>9750</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0.842000007629395</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H2099" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61249,6 +61249,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2100">
+      <c r="A2100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2100" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>7050</v>
+      </c>
+      <c r="I2100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2101" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>0.797999978065491</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0.797999978065491</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="H2101" t="n">
+        <v>13350</v>
+      </c>
+      <c r="I2101" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61307,6 +61307,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2102">
+      <c r="A2102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2102" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>0.745999991893768</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>0.727999985218048</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="H2102" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I2102" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61336,6 +61336,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2103">
+      <c r="A2103" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2103" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I2103" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61365,6 +61365,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2104">
+      <c r="A2104" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2104" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>0.736000001430511</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0.736000001430511</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I2104" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61394,6 +61394,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2105">
+      <c r="A2105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2105" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>19350</v>
+      </c>
+      <c r="I2105" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61423,6 +61423,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2106">
+      <c r="A2106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2106" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>7050</v>
+      </c>
+      <c r="I2106" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61452,6 +61452,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2107">
+      <c r="A2107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2107" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I2107" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61481,6 +61481,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2108">
+      <c r="A2108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2108" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>0.708000004291534</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>0.708000004291534</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>5100</v>
+      </c>
+      <c r="I2108" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/POR.MI.xlsx
+++ b/data/POR.MI.xlsx
@@ -61510,6 +61510,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2109">
+      <c r="A2109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2109" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>0.759999990463257</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>0.759999990463257</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I2109" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
